--- a/.schema/MHR_USER_POS.xlsx
+++ b/.schema/MHR_USER_POS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_fuk\git\sample\.schema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B0CBEC-957A-487D-8A5B-215C4E07B682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MHR_USER_POS" sheetId="1" r:id="rId1"/>
@@ -488,19 +488,19 @@
       </c>
       <c r="D3" s="3">
         <f t="shared" ref="D3:D12" ca="1" si="0">NOW()</f>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="3">
         <f t="shared" ref="F3:F12" ca="1" si="1">NOW()</f>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" ref="H3:H12" ca="1" si="2">NOW()</f>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -518,19 +518,19 @@
       </c>
       <c r="D4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
@@ -548,19 +548,19 @@
       </c>
       <c r="D5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
@@ -578,19 +578,19 @@
       </c>
       <c r="D6" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
@@ -608,19 +608,19 @@
       </c>
       <c r="D7" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
@@ -638,19 +638,19 @@
       </c>
       <c r="D8" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
@@ -668,19 +668,19 @@
       </c>
       <c r="D9" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
@@ -698,19 +698,19 @@
       </c>
       <c r="D10" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>
@@ -728,19 +728,19 @@
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
@@ -758,19 +758,19 @@
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46250.455865162039</v>
+        <v>46282.559260532405</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>

--- a/.schema/MHR_USER_POS.xlsx
+++ b/.schema/MHR_USER_POS.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B0CBEC-957A-487D-8A5B-215C4E07B682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914F05E2-E228-4F59-A2E6-1E9AA279C2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57600" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MHR_USER_POS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMARF.MHR_USER_POS!$A$2:$I$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">EMARF.MHR_USER_POS!$2:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMARF.MHR_USER_POS!$A$1:$I$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">EMARF.MHR_USER_POS!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -74,7 +74,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +100,12 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -149,7 +155,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -170,6 +176,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" textRotation="180"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -433,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="3" width="6.5" style="1" bestFit="1" customWidth="1"/>
@@ -446,61 +458,90 @@
     <col min="10" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.2" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5" t="s">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <f t="shared" ref="D2:D65" ca="1" si="0">NOW()</f>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="3">
+        <f t="shared" ref="F2:F65" ca="1" si="1">NOW()</f>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <f t="shared" ref="H2:H65" ca="1" si="2">NOW()</f>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3">
-        <f t="shared" ref="D3:D12" ca="1" si="0">NOW()</f>
-        <v>46282.559260532405</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="3">
-        <f t="shared" ref="F3:F12" ca="1" si="1">NOW()</f>
-        <v>46282.559260532405</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H12" ca="1" si="2">NOW()</f>
-        <v>46282.559260532405</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -508,29 +549,29 @@
     </row>
     <row r="4" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
@@ -538,29 +579,29 @@
     </row>
     <row r="5" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
@@ -568,29 +609,29 @@
     </row>
     <row r="6" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
@@ -598,29 +639,29 @@
     </row>
     <row r="7" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
-        <v>30</v>
-      </c>
       <c r="C7" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
@@ -628,29 +669,29 @@
     </row>
     <row r="8" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
@@ -658,29 +699,29 @@
     </row>
     <row r="9" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
@@ -688,29 +729,29 @@
     </row>
     <row r="10" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>
@@ -718,66 +759,1926 @@
     </row>
     <row r="11" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C11" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
-      <c r="A12" s="2">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2">
-        <v>35</v>
-      </c>
-      <c r="C12" s="2">
-        <v>10</v>
+    <row r="12" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="7">
+        <v>1</v>
+      </c>
+      <c r="B12" s="8">
+        <v>14</v>
+      </c>
+      <c r="C12" s="8">
+        <v>11</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46282.559260532405</v>
+        <v>46316.444081828704</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
       </c>
     </row>
+    <row r="13" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="7">
+        <v>2</v>
+      </c>
+      <c r="B13" s="8">
+        <v>20</v>
+      </c>
+      <c r="C13" s="8">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="7">
+        <v>3</v>
+      </c>
+      <c r="B14" s="8">
+        <v>22</v>
+      </c>
+      <c r="C14" s="8">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="7">
+        <v>4</v>
+      </c>
+      <c r="B15" s="8">
+        <v>22</v>
+      </c>
+      <c r="C15" s="8">
+        <v>14</v>
+      </c>
+      <c r="D15" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="7">
+        <v>5</v>
+      </c>
+      <c r="B16" s="8">
+        <v>22</v>
+      </c>
+      <c r="C16" s="8">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="7">
+        <v>6</v>
+      </c>
+      <c r="B17" s="8">
+        <v>23</v>
+      </c>
+      <c r="C17" s="8">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="7">
+        <v>7</v>
+      </c>
+      <c r="B18" s="8">
+        <v>23</v>
+      </c>
+      <c r="C18" s="8">
+        <v>17</v>
+      </c>
+      <c r="D18" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="7">
+        <v>8</v>
+      </c>
+      <c r="B19" s="8">
+        <v>23</v>
+      </c>
+      <c r="C19" s="8">
+        <v>18</v>
+      </c>
+      <c r="D19" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="7">
+        <v>9</v>
+      </c>
+      <c r="B20" s="8">
+        <v>23</v>
+      </c>
+      <c r="C20" s="8">
+        <v>19</v>
+      </c>
+      <c r="D20" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="7">
+        <v>10</v>
+      </c>
+      <c r="B21" s="8">
+        <v>23</v>
+      </c>
+      <c r="C21" s="8">
+        <v>20</v>
+      </c>
+      <c r="D21" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="7">
+        <v>11</v>
+      </c>
+      <c r="B22" s="8">
+        <v>23</v>
+      </c>
+      <c r="C22" s="8">
+        <v>21</v>
+      </c>
+      <c r="D22" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="7">
+        <v>12</v>
+      </c>
+      <c r="B23" s="8">
+        <v>23</v>
+      </c>
+      <c r="C23" s="8">
+        <v>22</v>
+      </c>
+      <c r="D23" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="7">
+        <v>13</v>
+      </c>
+      <c r="B24" s="8">
+        <v>25</v>
+      </c>
+      <c r="C24" s="8">
+        <v>23</v>
+      </c>
+      <c r="D24" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="7">
+        <v>14</v>
+      </c>
+      <c r="B25" s="8">
+        <v>25</v>
+      </c>
+      <c r="C25" s="8">
+        <v>24</v>
+      </c>
+      <c r="D25" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="7">
+        <v>15</v>
+      </c>
+      <c r="B26" s="8">
+        <v>25</v>
+      </c>
+      <c r="C26" s="8">
+        <v>25</v>
+      </c>
+      <c r="D26" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="7">
+        <v>16</v>
+      </c>
+      <c r="B27" s="8">
+        <v>25</v>
+      </c>
+      <c r="C27" s="8">
+        <v>26</v>
+      </c>
+      <c r="D27" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="7">
+        <v>17</v>
+      </c>
+      <c r="B28" s="8">
+        <v>25</v>
+      </c>
+      <c r="C28" s="8">
+        <v>27</v>
+      </c>
+      <c r="D28" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="7">
+        <v>18</v>
+      </c>
+      <c r="B29" s="8">
+        <v>25</v>
+      </c>
+      <c r="C29" s="8">
+        <v>28</v>
+      </c>
+      <c r="D29" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="7">
+        <v>19</v>
+      </c>
+      <c r="B30" s="8">
+        <v>25</v>
+      </c>
+      <c r="C30" s="8">
+        <v>29</v>
+      </c>
+      <c r="D30" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="7">
+        <v>20</v>
+      </c>
+      <c r="B31" s="8">
+        <v>25</v>
+      </c>
+      <c r="C31" s="8">
+        <v>30</v>
+      </c>
+      <c r="D31" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="7">
+        <v>21</v>
+      </c>
+      <c r="B32" s="8">
+        <v>25</v>
+      </c>
+      <c r="C32" s="8">
+        <v>31</v>
+      </c>
+      <c r="D32" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="7">
+        <v>22</v>
+      </c>
+      <c r="B33" s="8">
+        <v>25</v>
+      </c>
+      <c r="C33" s="8">
+        <v>32</v>
+      </c>
+      <c r="D33" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E33" s="4"/>
+      <c r="F33" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="7">
+        <v>23</v>
+      </c>
+      <c r="B34" s="8">
+        <v>25</v>
+      </c>
+      <c r="C34" s="8">
+        <v>33</v>
+      </c>
+      <c r="D34" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G34" s="2">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="7">
+        <v>24</v>
+      </c>
+      <c r="B35" s="8">
+        <v>25</v>
+      </c>
+      <c r="C35" s="8">
+        <v>34</v>
+      </c>
+      <c r="D35" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="7">
+        <v>25</v>
+      </c>
+      <c r="B36" s="8">
+        <v>25</v>
+      </c>
+      <c r="C36" s="8">
+        <v>35</v>
+      </c>
+      <c r="D36" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="7">
+        <v>26</v>
+      </c>
+      <c r="B37" s="8">
+        <v>25</v>
+      </c>
+      <c r="C37" s="8">
+        <v>36</v>
+      </c>
+      <c r="D37" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="7">
+        <v>27</v>
+      </c>
+      <c r="B38" s="8">
+        <v>25</v>
+      </c>
+      <c r="C38" s="8">
+        <v>37</v>
+      </c>
+      <c r="D38" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="7">
+        <v>28</v>
+      </c>
+      <c r="B39" s="8">
+        <v>25</v>
+      </c>
+      <c r="C39" s="8">
+        <v>38</v>
+      </c>
+      <c r="D39" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G39" s="2">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I39" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="7">
+        <v>29</v>
+      </c>
+      <c r="B40" s="8">
+        <v>25</v>
+      </c>
+      <c r="C40" s="8">
+        <v>39</v>
+      </c>
+      <c r="D40" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="7">
+        <v>30</v>
+      </c>
+      <c r="B41" s="8">
+        <v>26</v>
+      </c>
+      <c r="C41" s="8">
+        <v>40</v>
+      </c>
+      <c r="D41" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I41" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="7">
+        <v>31</v>
+      </c>
+      <c r="B42" s="8">
+        <v>26</v>
+      </c>
+      <c r="C42" s="8">
+        <v>41</v>
+      </c>
+      <c r="D42" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G42" s="2">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="7">
+        <v>32</v>
+      </c>
+      <c r="B43" s="8">
+        <v>26</v>
+      </c>
+      <c r="C43" s="8">
+        <v>42</v>
+      </c>
+      <c r="D43" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="7">
+        <v>33</v>
+      </c>
+      <c r="B44" s="8">
+        <v>26</v>
+      </c>
+      <c r="C44" s="8">
+        <v>43</v>
+      </c>
+      <c r="D44" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G44" s="2">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I44" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="7">
+        <v>34</v>
+      </c>
+      <c r="B45" s="8">
+        <v>26</v>
+      </c>
+      <c r="C45" s="8">
+        <v>44</v>
+      </c>
+      <c r="D45" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G45" s="2">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="7">
+        <v>35</v>
+      </c>
+      <c r="B46" s="8">
+        <v>26</v>
+      </c>
+      <c r="C46" s="8">
+        <v>45</v>
+      </c>
+      <c r="D46" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="7">
+        <v>36</v>
+      </c>
+      <c r="B47" s="8">
+        <v>26</v>
+      </c>
+      <c r="C47" s="8">
+        <v>46</v>
+      </c>
+      <c r="D47" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G47" s="2">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="7">
+        <v>37</v>
+      </c>
+      <c r="B48" s="8">
+        <v>26</v>
+      </c>
+      <c r="C48" s="8">
+        <v>47</v>
+      </c>
+      <c r="D48" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G48" s="2">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="7">
+        <v>38</v>
+      </c>
+      <c r="B49" s="8">
+        <v>26</v>
+      </c>
+      <c r="C49" s="8">
+        <v>48</v>
+      </c>
+      <c r="D49" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G49" s="2">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="7">
+        <v>39</v>
+      </c>
+      <c r="B50" s="8">
+        <v>26</v>
+      </c>
+      <c r="C50" s="8">
+        <v>49</v>
+      </c>
+      <c r="D50" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G50" s="2">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I50" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="7">
+        <v>40</v>
+      </c>
+      <c r="B51" s="8">
+        <v>26</v>
+      </c>
+      <c r="C51" s="8">
+        <v>50</v>
+      </c>
+      <c r="D51" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G51" s="2">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I51" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="7">
+        <v>41</v>
+      </c>
+      <c r="B52" s="8">
+        <v>26</v>
+      </c>
+      <c r="C52" s="8">
+        <v>51</v>
+      </c>
+      <c r="D52" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G52" s="2">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="7">
+        <v>42</v>
+      </c>
+      <c r="B53" s="8">
+        <v>26</v>
+      </c>
+      <c r="C53" s="8">
+        <v>52</v>
+      </c>
+      <c r="D53" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G53" s="2">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I53" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="7">
+        <v>43</v>
+      </c>
+      <c r="B54" s="8">
+        <v>26</v>
+      </c>
+      <c r="C54" s="8">
+        <v>53</v>
+      </c>
+      <c r="D54" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G54" s="2">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I54" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="7">
+        <v>44</v>
+      </c>
+      <c r="B55" s="8">
+        <v>26</v>
+      </c>
+      <c r="C55" s="8">
+        <v>54</v>
+      </c>
+      <c r="D55" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G55" s="2">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I55" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="7">
+        <v>45</v>
+      </c>
+      <c r="B56" s="8">
+        <v>26</v>
+      </c>
+      <c r="C56" s="8">
+        <v>55</v>
+      </c>
+      <c r="D56" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G56" s="2">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I56" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="7">
+        <v>46</v>
+      </c>
+      <c r="B57" s="8">
+        <v>26</v>
+      </c>
+      <c r="C57" s="8">
+        <v>56</v>
+      </c>
+      <c r="D57" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G57" s="2">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I57" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="7">
+        <v>30</v>
+      </c>
+      <c r="B58" s="8">
+        <v>28</v>
+      </c>
+      <c r="C58" s="8">
+        <v>57</v>
+      </c>
+      <c r="D58" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G58" s="2">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I58" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="7">
+        <v>31</v>
+      </c>
+      <c r="B59" s="8">
+        <v>28</v>
+      </c>
+      <c r="C59" s="8">
+        <v>58</v>
+      </c>
+      <c r="D59" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G59" s="2">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I59" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="7">
+        <v>32</v>
+      </c>
+      <c r="B60" s="8">
+        <v>28</v>
+      </c>
+      <c r="C60" s="8">
+        <v>59</v>
+      </c>
+      <c r="D60" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G60" s="2">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I60" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="7">
+        <v>33</v>
+      </c>
+      <c r="B61" s="8">
+        <v>28</v>
+      </c>
+      <c r="C61" s="8">
+        <v>60</v>
+      </c>
+      <c r="D61" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G61" s="2">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I61" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="7">
+        <v>34</v>
+      </c>
+      <c r="B62" s="8">
+        <v>28</v>
+      </c>
+      <c r="C62" s="8">
+        <v>61</v>
+      </c>
+      <c r="D62" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G62" s="2">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I62" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="7">
+        <v>35</v>
+      </c>
+      <c r="B63" s="8">
+        <v>28</v>
+      </c>
+      <c r="C63" s="8">
+        <v>62</v>
+      </c>
+      <c r="D63" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G63" s="2">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I63" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="7">
+        <v>36</v>
+      </c>
+      <c r="B64" s="8">
+        <v>28</v>
+      </c>
+      <c r="C64" s="8">
+        <v>63</v>
+      </c>
+      <c r="D64" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G64" s="2">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I64" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="7">
+        <v>37</v>
+      </c>
+      <c r="B65" s="8">
+        <v>28</v>
+      </c>
+      <c r="C65" s="8">
+        <v>64</v>
+      </c>
+      <c r="D65" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G65" s="2">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I65" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="7">
+        <v>38</v>
+      </c>
+      <c r="B66" s="8">
+        <v>28</v>
+      </c>
+      <c r="C66" s="8">
+        <v>65</v>
+      </c>
+      <c r="D66" s="3">
+        <f t="shared" ref="D66:D74" ca="1" si="3">NOW()</f>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="3">
+        <f t="shared" ref="F66:F74" ca="1" si="4">NOW()</f>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G66" s="2">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3">
+        <f t="shared" ref="H66:H74" ca="1" si="5">NOW()</f>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I66" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A67" s="7">
+        <v>39</v>
+      </c>
+      <c r="B67" s="8">
+        <v>28</v>
+      </c>
+      <c r="C67" s="8">
+        <v>66</v>
+      </c>
+      <c r="D67" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E67" s="4"/>
+      <c r="F67" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G67" s="2">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I67" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="7">
+        <v>40</v>
+      </c>
+      <c r="B68" s="8">
+        <v>28</v>
+      </c>
+      <c r="C68" s="8">
+        <v>67</v>
+      </c>
+      <c r="D68" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G68" s="2">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I68" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A69" s="7">
+        <v>41</v>
+      </c>
+      <c r="B69" s="8">
+        <v>28</v>
+      </c>
+      <c r="C69" s="8">
+        <v>68</v>
+      </c>
+      <c r="D69" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G69" s="2">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I69" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A70" s="7">
+        <v>42</v>
+      </c>
+      <c r="B70" s="8">
+        <v>28</v>
+      </c>
+      <c r="C70" s="8">
+        <v>69</v>
+      </c>
+      <c r="D70" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G70" s="2">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I70" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="7">
+        <v>43</v>
+      </c>
+      <c r="B71" s="8">
+        <v>28</v>
+      </c>
+      <c r="C71" s="8">
+        <v>70</v>
+      </c>
+      <c r="D71" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G71" s="2">
+        <v>0</v>
+      </c>
+      <c r="H71" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I71" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A72" s="7">
+        <v>44</v>
+      </c>
+      <c r="B72" s="8">
+        <v>28</v>
+      </c>
+      <c r="C72" s="8">
+        <v>71</v>
+      </c>
+      <c r="D72" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G72" s="2">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I72" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A73" s="7">
+        <v>45</v>
+      </c>
+      <c r="B73" s="8">
+        <v>28</v>
+      </c>
+      <c r="C73" s="8">
+        <v>72</v>
+      </c>
+      <c r="D73" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G73" s="2">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I73" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A74" s="7">
+        <v>46</v>
+      </c>
+      <c r="B74" s="8">
+        <v>28</v>
+      </c>
+      <c r="C74" s="8">
+        <v>73</v>
+      </c>
+      <c r="D74" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="G74" s="2">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>46316.444081828704</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
